--- a/aReport_card/2025_2026/Second_term/JSS3/Second_term_JSS3_Business_Studies.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS3/Second_term_JSS3_Business_Studies.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81293619-9CB7-405B-880E-A29AE43534D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E05394C-FC56-4D38-92C3-691495F8F836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,17 +493,17 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <f t="shared" ref="F2:F9" si="0">SUM(C2:E2)</f>
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -514,17 +514,17 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -535,17 +535,17 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -556,17 +556,17 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -577,17 +577,17 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -598,17 +598,17 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -619,17 +619,17 @@
         <v>19</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -640,17 +640,17 @@
         <v>21</v>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
